--- a/AAII_Financials/Quarterly/BACHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BACHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>BACHY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2126,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>239583200</v>
+      </c>
+      <c r="E41" s="3">
         <v>96675000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>287641700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72148100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>217540000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>86395400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>284854300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76029400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>316861500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>119287600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>319999400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101408600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>211389200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109372000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>275857200</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>246674700</v>
+      </c>
+      <c r="E42" s="3">
         <v>341398600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>229652900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>320487700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>207119800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>270810600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>196945900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>279016000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>191301700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>280723900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>192256600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>286633000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>176582500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>328397800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>201107300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
+        <v>43447800</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>35762800</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>42162100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>33381400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>36397900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>25777700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>112185100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>32801400</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>254500</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>262900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>282800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>298300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>398100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>444500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>276500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>312200</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>56995100</v>
+      </c>
+      <c r="E45" s="3">
         <v>47150400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50797500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29136800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26055700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14509500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31948900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18671900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26909500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14087400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21625700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13096000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19613600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13432100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25954300</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>827182500</v>
+      </c>
+      <c r="E46" s="3">
         <v>800976300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>830737200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>728528200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>706052200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>689448600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>759366400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>719099200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>794749900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>798947600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>795399000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>737784400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>747580600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>807028300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>760958200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1469649800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1389380300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1320426800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1266644400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1233785800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1154124300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1104763200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1074718100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>978314400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>959882400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>971737300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>897762200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>887092500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>896147400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>885135000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41419700</v>
+      </c>
+      <c r="E48" s="3">
         <v>37748300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39440000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34716000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36565800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33726500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36182800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33601500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35578400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33743800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37574800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34369000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37483300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35151800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38580600</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>5192000</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>5019600</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>4460300</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>4385300</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>4138800</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>4103900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>3855900</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>3980900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14914200</v>
+      </c>
+      <c r="E52" s="3">
         <v>42776000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12139000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>33145900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12189500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>33718700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12032000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39683200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13513300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38231100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14701800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34087100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15257400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34736800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14927500</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5916021500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5740452500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5484112400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5274491900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5135628200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4959298100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4803509900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4856937500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4665987800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4661594900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4573772900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4353372800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4286259500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4423469000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4189170700</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3906195100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3939437600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3691814500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3606983900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3528506000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3529318400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3266816000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3380231000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3209682800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3338548300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3187583400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3109536600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3057475100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3190781500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2891048500</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1154299400</v>
+      </c>
+      <c r="E58" s="3">
         <v>19258300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>978539300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15839800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>837430100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17166400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>805952900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19226000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>764521000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19490900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>709313100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>22717400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>594541900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16210600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>670236000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36599900</v>
+      </c>
+      <c r="E59" s="3">
         <v>13974100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30636500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14466700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30710000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10529700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39201100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11464500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35579000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9475500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25079500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12448000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34693100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13296000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26199000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5146858600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3972670000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4760621800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3637290400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4453405700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3557014500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4168789600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3410921500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4057842400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3367514700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3972227900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3144702100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3730182300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3220288100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3632189000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>181170900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1163674300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161469000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1057972700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>150780000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>878707200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>142746400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>916970800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>142379400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>801777300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>129656700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>736700700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>108174500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>721779400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>104544300</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>108116500</v>
+      </c>
+      <c r="E62" s="3">
         <v>131531400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>100604300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>122910000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>92556500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>113069400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>84969200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>117835600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>81081100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>105421900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>80858400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>102041800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>78733600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>99008500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>78586200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5438989400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5269589300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5025442100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4819761900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4699314300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4550322300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4398944400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4447217200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4283572200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4275999400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4184990800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3984693300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3919236200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4042402200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3817527000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,55 +3484,61 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>14716900</v>
+      </c>
+      <c r="E70" s="3">
         <v>14493700</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>14292700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>14042200</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>13954700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>13776500</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>16378700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>17043300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>16451300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>16557000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>16859600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>16384300</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>16484400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>17403800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>17333100</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>311707700</v>
+      </c>
+      <c r="E72" s="3">
         <v>303941300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>291624900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>282794400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>272739600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>266735500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>257743300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>264870500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>247804700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>251932000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>248933400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>234798000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>228682300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>243783100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>234706300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>441745100</v>
+      </c>
+      <c r="E76" s="3">
         <v>435437800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>423778300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>420512600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>403085100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>375714700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>369453900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>373876500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>348053600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>350936500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>353969200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>335219000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>330366100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>343176500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>334109900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>969900</v>
+      </c>
+      <c r="E83" s="3">
         <v>956200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>172500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1035600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1007200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1005200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>217900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1047500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1064500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1062600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>351600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1008000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1076100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>406400</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>93552000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-120575100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37300600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3795400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7564800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200268400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11850900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26165800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>58643000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-166908500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17469900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-50958100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-50800300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-179043600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10585500</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2384100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1711700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3298500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1642600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1589400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-705800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1555800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1349300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-535200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-349800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1476400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-830800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1156500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-615800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2481400</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52722300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58806900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34177200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26021300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38665100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-51081200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1469800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-93752500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1523500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20499400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36753600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2745900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11245400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25799400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17383900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1769800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3294500</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>4997100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4900700</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>9921300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>9360200</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-32574500</v>
+      </c>
+      <c r="E100" s="3">
         <v>121678600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>45277800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>46192100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>38645800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>171355600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>62498400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-151300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-51120700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>174664500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>49508900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>62021100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>48388900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>237002900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>53619600</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3464100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2125300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-93800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>502200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>164000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2460000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7632300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1520300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-854800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8492500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7910500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1758700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3142800</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4857900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61920900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45927200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14168000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11009700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-77868800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>52023400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-67235700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6162900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13943600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30425500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5857000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6024400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30639700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>45966300</v>
       </c>
     </row>
